--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
   <si>
     <t>Filename</t>
   </si>
@@ -808,685 +808,691 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9979,0.0005,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9241,0.0006,0.0000,0.0335</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9961,0.0010,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.9940,0.0001,0.0001,0.0033</t>
+  </si>
+  <si>
+    <t>0.0717,0.0001,0.0004,0.9810</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.1817,0.0009,0.8690,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.0009,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.1128,0.0010,0.9321,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.9798,0.0013,0.0143,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.9952,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0832,0.0012,0.9204,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.0003,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0001,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9985,0.0004</t>
+  </si>
+  <si>
+    <t>0.0088,0.0006,0.9928,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0425,0.9495,0.0036,0.0010</t>
+  </si>
+  <si>
+    <t>0.1045,0.0264,0.8980,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.0045,0.9984,0.0064</t>
+  </si>
+  <si>
+    <t>0.0005,0.9974,0.0056,0.0002</t>
+  </si>
+  <si>
+    <t>0.9929,0.0041,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.7977,0.0621,0.0403,0.0008</t>
+  </si>
+  <si>
+    <t>0.8939,0.1291,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.9857,0.0172,0.0005</t>
+  </si>
+  <si>
+    <t>0.0102,0.6584,0.1264,0.0037</t>
+  </si>
+  <si>
+    <t>0.0147,0.0006,0.9287,0.0181</t>
+  </si>
+  <si>
+    <t>0.0025,0.0063,0.9916,0.0011</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9985,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.0151,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0089,0.3961,0.0015,0.9535</t>
+  </si>
+  <si>
+    <t>0.0024,0.9952,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0038,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0037,0.9937,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0181,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9843,0.0202,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0042,0.9985,0.0016</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0025,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0054,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9835,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0022,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9855,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9952,0.0001,0.0052,0.0001</t>
+  </si>
+  <si>
+    <t>0.9352,0.0002,0.1121,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9938,0.9516,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9924,0.9831,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0215,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9797,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0000,0.0013,0.9980</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0084,0.9987</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.0007,0.9995</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.9692,0.9569,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9801,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9650,0.9888,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.1148,0.9903,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9904,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.8485,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0022,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.0009,0.9962,0.0021</t>
+  </si>
+  <si>
+    <t>0.9969,0.0002,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9988,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0800,0.9298,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.0741,0.0323,0.8259,0.0005</t>
+  </si>
+  <si>
+    <t>0.9561,0.0004,0.0519,0.0001</t>
+  </si>
+  <si>
+    <t>0.5400,0.0609,0.0803,0.0023</t>
+  </si>
+  <si>
+    <t>0.3109,0.2050,0.0773,0.0102</t>
+  </si>
+  <si>
+    <t>0.0043,0.0113,0.0190,0.9810</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9578,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8320,0.1841,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0703,0.9479,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.4925,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.4213,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9973,0.0003</t>
+  </si>
+  <si>
+    <t>0.9940,0.0002,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.7963,0.0012,0.2157,0.0005</t>
+  </si>
+  <si>
+    <t>0.1092,0.0002,0.9539,0.0001</t>
+  </si>
+  <si>
+    <t>0.2718,0.0006,0.7973,0.0002</t>
+  </si>
+  <si>
+    <t>0.1796,0.0001,0.0000,0.9493</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0018,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.9960,0.9501,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.9960,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9955,0.0015,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.8143,0.2484,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5848,0.0005,0.0001,0.5605</t>
+  </si>
+  <si>
+    <t>0.0010,0.0040,0.9976,0.0011</t>
+  </si>
+  <si>
+    <t>0.9695,0.0002,0.0034,0.0224</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0466,0.9458,0.0042,0.0011</t>
+  </si>
+  <si>
+    <t>0.9828,0.0055,0.0040,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0899,0.8831,0.0062,0.0006</t>
+  </si>
+  <si>
+    <t>0.9642,0.0014,0.0255,0.0002</t>
+  </si>
+  <si>
+    <t>0.9390,0.0363,0.0076,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9396,0.0648,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.3609,0.7301,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.8123,0.2230,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.8799,0.0039,0.1553,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8193,0.2342,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0034,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9743,0.0122,0.0058,0.0015</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6591,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0596,0.9956,0.0007</t>
+  </si>
+  <si>
+    <t>0.0020,0.0015,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0672,0.0005,0.9667,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.0014,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.1140,0.0010,0.9293,0.0002</t>
+  </si>
+  <si>
+    <t>0.9224,0.0033,0.0368,0.0017</t>
+  </si>
+  <si>
+    <t>0.0048,0.0004,0.9940,0.0002</t>
+  </si>
+  <si>
+    <t>0.1131,0.0553,0.6666,0.0004</t>
+  </si>
+  <si>
+    <t>0.2482,0.0030,0.7529,0.0003</t>
+  </si>
+  <si>
+    <t>0.6641,0.0010,0.3244,0.0014</t>
+  </si>
+  <si>
+    <t>0.8069,0.0004,0.2067,0.0006</t>
+  </si>
+  <si>
+    <t>0.0285,0.9716,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.9983,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1013,0.9316,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.7576,0.3280,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0886,0.9441,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9920,0.0029,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0002,0.0054,0.0001</t>
+  </si>
+  <si>
+    <t>0.9745,0.0022,0.0050,0.0015</t>
+  </si>
+  <si>
+    <t>0.1157,0.0034,0.8849,0.0006</t>
+  </si>
+  <si>
+    <t>0.0445,0.0002,0.9665,0.0004</t>
+  </si>
+  <si>
+    <t>0.0112,0.0007,0.9887,0.0020</t>
+  </si>
+  <si>
+    <t>0.0004,0.0014,0.9982,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0094,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.0027,0.0026,0.9907,0.0015</t>
+  </si>
+  <si>
+    <t>0.0010,0.0025,0.9957,0.0006</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0065,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9540,0.0750,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0221,0.0317,0.9403,0.0056</t>
+  </si>
+  <si>
+    <t>0.6279,0.0012,0.4637,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0774,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0022,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0061,0.0025,0.9871,0.0019</t>
+  </si>
+  <si>
+    <t>0.1992,0.0004,0.8055,0.0017</t>
+  </si>
+  <si>
+    <t>0.2947,0.0001,0.7780,0.0007</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9864,0.0103,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
     <t>0.9996,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9791,0.0003,0.0187,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0005,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.7587,0.0010,0.3959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0002,0.9953,0.0001</t>
-  </si>
-  <si>
-    <t>0.8734,0.0019,0.1280,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0283,0.9819,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9548,0.0001,0.0637,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.0003,0.9922,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0001,0.9960,0.0004</t>
-  </si>
-  <si>
-    <t>0.0128,0.0002,0.9927,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0533,0.9612,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9841,0.0132,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9993,0.0463</t>
-  </si>
-  <si>
-    <t>0.0011,0.9626,0.2366,0.0006</t>
-  </si>
-  <si>
-    <t>0.9925,0.0047,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9936,0.0049,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.8424,0.2394,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9966,0.0511,0.0002</t>
-  </si>
-  <si>
-    <t>0.0030,0.1265,0.7410,0.0102</t>
-  </si>
-  <si>
-    <t>0.0071,0.0013,0.9820,0.0058</t>
-  </si>
-  <si>
-    <t>0.0012,0.0044,0.9950,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0040,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0043,0.0004,0.9922,0.0005</t>
-  </si>
-  <si>
-    <t>0.0224,0.5521,0.0004,0.6469</t>
-  </si>
-  <si>
-    <t>0.0017,0.9931,0.0087,0.0029</t>
-  </si>
-  <si>
-    <t>0.0002,0.9980,0.0729,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0054,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0035,0.9933,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0002,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0018,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9923,0.0065,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.0050,0.0014,0.9959,0.0015</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0057,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9853,0.9850,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9992,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9911,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6988,0.0001,0.4920,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0005,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0015,0.9997,0.0022</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.9844,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9935,0.9849,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9543,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0000,0.0024,0.9975</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0166,0.9969</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.0003,0.9992</t>
+    <t>0.9988,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0093,0.0045,0.9786,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0012,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.0074,0.9920,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.0003,0.9910,0.0048</t>
+  </si>
+  <si>
+    <t>0.0179,0.0054,0.9657,0.0019</t>
+  </si>
+  <si>
+    <t>0.0725,0.0008,0.8929,0.0058</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0038,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0940,0.0002,0.0010,0.9642</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9973,0.9632,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9910,0.9670,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.5469,0.9776,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.1870,0.9819,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.8518,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.8685,0.8595,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0021,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9993,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.9942,0.0002,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0178,0.0005,0.9864,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1713,0.8741,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.7880,0.0032,0.1929,0.0003</t>
-  </si>
-  <si>
-    <t>0.9848,0.0005,0.0107,0.0001</t>
-  </si>
-  <si>
-    <t>0.1016,0.0181,0.8150,0.0018</t>
-  </si>
-  <si>
-    <t>0.1227,0.1778,0.2415,0.0074</t>
-  </si>
-  <si>
-    <t>0.0081,0.0100,0.0123,0.9880</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9482,0.0489,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.6135,0.4210,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0003,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0013,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0220,0.9898,0.0015</t>
-  </si>
-  <si>
-    <t>0.0015,0.0822,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0089,0.0041,0.9771,0.0005</t>
-  </si>
-  <si>
-    <t>0.9517,0.0001,0.0595,0.0002</t>
-  </si>
-  <si>
-    <t>0.3986,0.0030,0.5500,0.0016</t>
-  </si>
-  <si>
-    <t>0.0103,0.0004,0.9922,0.0002</t>
-  </si>
-  <si>
-    <t>0.9474,0.0008,0.0477,0.0004</t>
-  </si>
-  <si>
-    <t>0.0404,0.0001,0.0003,0.9874</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0019,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0036,0.0003,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.9940,0.9645,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0287,0.9789,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0018,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.8310,0.2536,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9564,0.0026,0.0034,0.0123</t>
-  </si>
-  <si>
-    <t>0.0008,0.0048,0.9980,0.0013</t>
-  </si>
-  <si>
-    <t>0.9748,0.0001,0.0101,0.0030</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0044,0.9929,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.9768,0.0085,0.0069,0.0007</t>
-  </si>
-  <si>
-    <t>0.9972,0.0004,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.6089,0.3808,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.2102,0.1039,0.3166,0.0004</t>
-  </si>
-  <si>
-    <t>0.9530,0.0274,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0011,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9862,0.0128,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.2588,0.7836,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.4936,0.5991,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9200,0.0322,0.0309,0.0016</t>
-  </si>
-  <si>
-    <t>0.9559,0.0622,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0015,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9981,0.0008,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0071,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.9912,0.0024,0.0040,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0736,0.9857,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0053,0.0239,0.9760,0.0021</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0001,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0024,0.9966,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0012,0.9980,0.0003</t>
-  </si>
-  <si>
-    <t>0.0166,0.0091,0.9595,0.0020</t>
-  </si>
-  <si>
-    <t>0.2805,0.0011,0.7386,0.0000</t>
-  </si>
-  <si>
-    <t>0.0330,0.8354,0.0352,0.0004</t>
-  </si>
-  <si>
-    <t>0.4361,0.0111,0.3962,0.0001</t>
-  </si>
-  <si>
-    <t>0.8992,0.0006,0.0708,0.0029</t>
-  </si>
-  <si>
-    <t>0.0132,0.0036,0.9795,0.0010</t>
-  </si>
-  <si>
-    <t>0.0355,0.9741,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.2379,0.8403,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.8939,0.1385,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0725,0.9504,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7374,0.1772,0.0033,0.0014</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9873,0.0020,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.0732,0.0089,0.9238,0.0007</t>
-  </si>
-  <si>
-    <t>0.1294,0.0022,0.8585,0.0031</t>
-  </si>
-  <si>
-    <t>0.0066,0.0008,0.9925,0.0015</t>
-  </si>
-  <si>
-    <t>0.0012,0.0044,0.9952,0.0007</t>
-  </si>
-  <si>
-    <t>0.0119,0.0764,0.9321,0.0051</t>
-  </si>
-  <si>
-    <t>0.0240,0.0020,0.9578,0.0029</t>
-  </si>
-  <si>
-    <t>0.0002,0.0021,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0005,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0112,0.0204,0.9704,0.0027</t>
-  </si>
-  <si>
-    <t>0.7900,0.0016,0.2255,0.0016</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9961,0.0130</t>
-  </si>
-  <si>
-    <t>0.0000,0.6358,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0008,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0040,0.9964,0.0014</t>
-  </si>
-  <si>
-    <t>0.9884,0.0003,0.0082,0.0001</t>
-  </si>
-  <si>
-    <t>0.2602,0.0002,0.8341,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0001,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0020,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0012,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0025,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0078,0.0071,0.9811,0.0015</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.0029,0.9913,0.0026</t>
-  </si>
-  <si>
-    <t>0.0219,0.0055,0.9672,0.0021</t>
-  </si>
-  <si>
-    <t>0.0056,0.0002,0.9916,0.0005</t>
-  </si>
-  <si>
-    <t>0.9626,0.0001,0.0007,0.0385</t>
-  </si>
-  <si>
-    <t>0.0009,0.0013,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.0123,0.0008,0.0003,0.9955</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.8335,0.0034,0.0093,0.0473</t>
+    <t>0.9904,0.0003,0.0003,0.0019</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1878,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1886,7 +1892,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1900,7 +1906,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1911,10 +1917,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1928,7 +1934,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1942,7 +1948,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2037,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>275</v>
@@ -2065,7 +2071,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>277</v>
@@ -2152,7 +2158,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2177,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2289,10 +2295,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2387,10 +2393,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2485,10 +2491,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>280</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2922,7 +2928,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3118,7 +3124,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3132,7 +3138,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>303</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3465,7 +3471,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
         <v>365</v>
@@ -3493,7 +3499,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
         <v>367</v>
@@ -3507,7 +3513,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
         <v>368</v>
@@ -3566,7 +3572,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>280</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3580,7 +3586,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3619,10 +3625,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>271</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3815,10 +3821,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3843,10 +3849,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3930,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3997,10 +4003,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4109,10 +4115,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4210,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>415</v>
+        <v>378</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4291,7 +4297,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>418</v>
@@ -4417,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
         <v>427</v>
@@ -4529,7 +4535,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
         <v>435</v>
@@ -4557,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>437</v>
@@ -4571,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>438</v>
@@ -4599,7 +4605,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
         <v>440</v>
@@ -4630,7 +4636,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>361</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4644,7 +4650,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4672,7 +4678,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4686,7 +4692,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4700,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4812,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>274</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>377</v>
+        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5005,10 +5011,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>314</v>
+        <v>468</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5089,10 +5095,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>318</v>
+        <v>476</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>476</v>
+        <v>350</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>482</v>
+        <v>312</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
